--- a/artfynd/A 11258-2023 artfynd.xlsx
+++ b/artfynd/A 11258-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11258-2023 artfynd.xlsx
+++ b/artfynd/A 11258-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,43 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>86039060</v>
+        <v>87864197</v>
       </c>
       <c r="B2" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>100090</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465077.7404102923</v>
+        <v>465078</v>
       </c>
       <c r="R2" t="n">
-        <v>6414794.22645981</v>
+        <v>6414794</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-06-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-06-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,7 +758,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94879428</v>
+        <v>101847102</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219875</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465077.7404102923</v>
+        <v>465078</v>
       </c>
       <c r="R3" t="n">
-        <v>6414794.22645981</v>
+        <v>6414794</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,22 +845,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-07-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-07-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,37 +878,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101847088</v>
+        <v>94879428</v>
       </c>
       <c r="B4" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465077.7404102923</v>
+        <v>465078</v>
       </c>
       <c r="R4" t="n">
-        <v>6414794.22645981</v>
+        <v>6414794</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,22 +947,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-06-24</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-06-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,57 +980,60 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101847102</v>
+        <v>102234314</v>
       </c>
       <c r="B5" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219875</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>råbyskogen, Sm</t>
+          <t>Råby blandskog, Råbyskogens naturreservat, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465077.7404102923</v>
+        <v>465091</v>
       </c>
       <c r="R5" t="n">
-        <v>6414794.22645981</v>
+        <v>6414811</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,22 +1057,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-06-24</t>
+          <t>2022-07-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-06-24</t>
+          <t>2022-07-13</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,77 +1088,64 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>henrik kullberg</t>
+          <t>Johan Wallander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>henrik kullberg</t>
+          <t>Johan Wallander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102234314</v>
+        <v>101847088</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Råby blandskog, Råbyskogens naturreservat, Sm</t>
+          <t>råbyskogen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465091.2049305392</v>
+        <v>465078</v>
       </c>
       <c r="R6" t="n">
-        <v>6414810.597266464</v>
+        <v>6414794</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,22 +1169,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2022-06-24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2022-06-24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,12 +1190,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Wallander</t>
+          <t>henrik kullberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Wallander</t>
+          <t>henrik kullberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1271,12 +1205,7 @@
         <v>102234323</v>
       </c>
       <c r="B7" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465091.2049305392</v>
+        <v>465091</v>
       </c>
       <c r="R7" t="n">
-        <v>6414810.597266464</v>
+        <v>6414811</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1394,6 +1323,108 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>86039060</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>råbyskogen, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>465078</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6414794</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skärstad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-06-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-06-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>henrik kullberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>henrik kullberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11258-2023 artfynd.xlsx
+++ b/artfynd/A 11258-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87864197</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101847102</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94879428</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102234314</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,6 +1224,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101847088</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102234323</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1425,8 +1460,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86039060</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>